--- a/04_DESIGN_TABLES/DesignTable_2700_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2700_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ25"/>
+  <dimension ref="A1:AQ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,35 +782,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2700-04-04</t>
+          <t>2700-02-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="C3" t="n">
-        <v>0.39837</v>
+        <v>0.32447</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.21875</v>
+        <v>0.15625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2608</v>
+        <v>0.19</v>
       </c>
       <c r="H3" t="n">
-        <v>0.182</v>
+        <v>0.125</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0795</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1135</v>
+        <v>0.1108</v>
       </c>
       <c r="K3" t="n">
         <v>60</v>
@@ -819,79 +819,79 @@
         <v>37</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4375</v>
+        <v>0.3125</v>
       </c>
       <c r="N3" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4538</v>
+        <v>0.367</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="R3" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="S3" t="n">
-        <v>0.21875</v>
+        <v>0.15625</v>
       </c>
       <c r="T3" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.182</v>
+        <v>0.125</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0795</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1135</v>
+        <v>0.1108</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4375</v>
+        <v>0.3125</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.1038</v>
+        <v>0.989</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.17</v>
+        <v>0.062</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.71</v>
+        <v>0.624</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.17</v>
+        <v>0.062</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.36</v>
+        <v>1.246</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2700-04-04</t>
+          <t>2700-02-02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 7/16-20 x 7/16-20 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 5/16-24 x 5/16-24 (bulkhead)</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>7/16-20</t>
+          <t>5/16-24</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7/16-20 (bulkhead)</t>
+          <t>5/16-24 (bulkhead)</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Air-Way s72 (double-pass 27 rows; first pass claimed 30 - trap; survey said 24 - page wins); JIC ends VERIFIED (MS33656J); -LN rows ship with locknut, same dims | MODEL: JIC end A: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); the bulkhead is the SECOND dash (I1 = the bulkhead length of that dash on 2705/2706, e.g. 2700-06-04 I1 1.20 = -04); bore step at the hex mid-plane (ASSUMPTION, as 2403)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L4@DRIVE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "L LGTH" = "1.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; C2HEX@HEX: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "C HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 12/13 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2700-06-04 0.69 vs 0.812); D1@BORE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "B1 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - bore end B1; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; D2@BORE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - bore end B2 (bulkhead); mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2700-02-02.stp (sha256 8510b8b0f1b648e7...) measured with wave2/straight/scripts/measure_bulkhead.py (prof.py section; validated: Brennan 2705-08-08 gives I1 1.44 = Air-Way): bulkhead tip 1.422 - relief start 0.352 (after the 0.04 collar) = 1.07; the -02 nose on the STEP = MS33656J JIC[2] (seat 0.1108, land 0.0662, relief 0.063); STEP overall 1.87 = catalog L 1.870, hex 0.5621 = catalog 0.562 [Brennan = yes 2026-10-18]; THDMAJ_B1@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (5/16-24); THDMAJ_B2@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (5/16-24); $PRP@Threads: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread texts, format of the built 2700 rows | MODEL: JIC end A: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); the bulkhead is the SECOND dash (I1 = the bulkhead length of that dash on 2705/2706, e.g. 2700-06-04 I1 1.20 = -04); bore step at the hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>bulkhead thread size/length and locknut geometry not tabulated on page - defer to MS51520 (untranscribed) or Brennan STEP -&gt; RESOLVED 2026-09-24 by the Brennan 2705-08-08 STEP: bulkhead thread = the JIC thread of that dash, run over the bulkhead length I1</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L4 / hex / bores from the Brennan TFA catalog p8, I1 measured on the Brennan 2700-02-02 STEP (no Air-Way -02 bulkhead)</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>2700-04-04</t>
+          <t>2700-02-02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2700-04-04-LN</t>
+          <t>2700-04-04</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2700-04-04-LN</t>
+          <t>2700-04-04</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 7/16-20 x 7/16-20 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 7/16-20 x 7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1077,36 +1077,36 @@
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>2700-LN-04-04</t>
+          <t>2700-04-04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2700-05-05</t>
+          <t>2700-04-04-LN</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>2.07</v>
       </c>
       <c r="C5" t="n">
-        <v>0.43301</v>
+        <v>0.39837</v>
       </c>
       <c r="D5" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="F5" t="n">
         <v>0.075</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2606</v>
+        <v>0.2608</v>
       </c>
       <c r="H5" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="I5" t="n">
         <v>0.0795</v>
@@ -1121,13 +1121,13 @@
         <v>37</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="N5" t="n">
         <v>0.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4536</v>
+        <v>0.4538</v>
       </c>
       <c r="P5" t="n">
         <v>0.02706</v>
@@ -1139,16 +1139,16 @@
         <v>0.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25</v>
+        <v>0.21875</v>
       </c>
       <c r="T5" t="n">
         <v>0.075</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9106</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>0.213</v>
+        <v>0.182</v>
       </c>
       <c r="W5" t="n">
         <v>0.0795</v>
@@ -1157,13 +1157,13 @@
         <v>0.1135</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5</v>
+        <v>0.4375</v>
       </c>
       <c r="Z5" t="n">
         <v>0.05</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.1036</v>
+        <v>1.1038</v>
       </c>
       <c r="AB5" t="n">
         <v>0.02706</v>
@@ -1175,25 +1175,25 @@
         <v>0.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AF5" t="n">
         <v>0.71</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.23</v>
+        <v>0.17</v>
       </c>
       <c r="AH5" t="n">
         <v>1.36</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2700-05-05</t>
+          <t>2700-04-04-LN</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1/2-20 x 1/2-20 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 7/16-20 x 7/16-20 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1/2-20</t>
+          <t>7/16-20</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1/2-20 (bulkhead)</t>
+          <t>7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
@@ -1228,14 +1228,14 @@
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>2700-05-05</t>
+          <t>2700-LN-04-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2700-05-05-LN</t>
+          <t>2700-05-05</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2700-05-05-LN</t>
+          <t>2700-05-05</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1/2-20 x 1/2-20 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1/2-20 x 1/2-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1379,42 +1379,42 @@
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>2700-LN-05-05</t>
+          <t>2700-05-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2700-06-04</t>
+          <t>2700-05-05-LN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="C7" t="n">
-        <v>0.39837</v>
+        <v>0.43301</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
-        <v>0.28125</v>
+        <v>0.25</v>
       </c>
       <c r="F7" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2515</v>
+        <v>0.2606</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2405</v>
+        <v>0.213</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="K7" t="n">
         <v>60</v>
@@ -1423,34 +1423,34 @@
         <v>37</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4495</v>
+        <v>0.4536</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="R7" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="S7" t="n">
-        <v>0.21875</v>
+        <v>0.25</v>
       </c>
       <c r="T7" t="n">
         <v>0.075</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9106</v>
       </c>
       <c r="V7" t="n">
-        <v>0.182</v>
+        <v>0.213</v>
       </c>
       <c r="W7" t="n">
         <v>0.0795</v>
@@ -1459,13 +1459,13 @@
         <v>0.1135</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4375</v>
+        <v>0.5</v>
       </c>
       <c r="Z7" t="n">
         <v>0.05</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.1038</v>
+        <v>1.1036</v>
       </c>
       <c r="AB7" t="n">
         <v>0.02706</v>
@@ -1477,25 +1477,25 @@
         <v>0.05</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.728</v>
+        <v>0.71</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.372</v>
+        <v>1.36</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2700-06-04</t>
+          <t>2700-05-05-LN</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 9/16-18 x 7/16-20 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1/2-20 x 1/2-20 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>9/16-18</t>
+          <t>1/2-20</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>7/16-20 (bulkhead)</t>
+          <t>1/2-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -1530,14 +1530,14 @@
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>2700-06-04</t>
+          <t>2700-LN-05-05</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2700-06-04-LN</t>
+          <t>2700-06-04</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2700-06-04-LN</t>
+          <t>2700-06-04</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 9/16-18 x 7/16-20 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 9/16-18 x 7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -1681,24 +1681,24 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>2700-LN-06-04</t>
+          <t>2700-06-04</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2700-06-06</t>
+          <t>2700-06-04-LN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.46765</v>
+        <v>0.39837</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E9" t="n">
         <v>0.28125</v>
@@ -1743,40 +1743,40 @@
         <v>0.05556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="T9" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9755</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="W9" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.1735</v>
+        <v>1.1038</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AE9" t="n">
         <v>0.3</v>
@@ -1785,19 +1785,19 @@
         <v>0.728</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.3</v>
+        <v>0.17</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.452</v>
+        <v>1.372</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2700-06-06</t>
+          <t>2700-06-04-LN</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 9/16-18 x 9/16-18 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 9/16-18 x 7/16-20 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9/16-18 (bulkhead)</t>
+          <t>7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -1832,14 +1832,14 @@
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>2700-06-06</t>
+          <t>2700-LN-06-04</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2700-06-06-LN</t>
+          <t>2700-06-06</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2700-06-06-LN</t>
+          <t>2700-06-06</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 9/16-18 x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 9/16-18 x 9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -1983,42 +1983,42 @@
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>2700-LN-06-06</t>
+          <t>2700-06-06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2700-08-08-LN</t>
+          <t>2700-06-06-LN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="C11" t="n">
-        <v>0.57735</v>
+        <v>0.46765</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="F11" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2837</v>
+        <v>0.2515</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="K11" t="n">
         <v>60</v>
@@ -2027,79 +2027,79 @@
         <v>37</v>
       </c>
       <c r="M11" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5367</v>
+        <v>0.4495</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="T11" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0667</v>
+        <v>0.9755</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.3197</v>
+        <v>1.1735</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.8285</v>
+        <v>0.728</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6115</v>
+        <v>1.452</v>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2700-08-08-LN</t>
+          <t>2700-06-06-LN</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 3/4-16 x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 9/16-18 x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3/4-16</t>
+          <t>9/16-18</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>3/4-16 (bulkhead)</t>
+          <t>9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -2134,39 +2134,39 @@
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>2700-LN-08-08</t>
+          <t>2700-LN-06-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2700-10-10</t>
+          <t>2700-08-08-LN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.74</v>
+        <v>2.44</v>
       </c>
       <c r="C12" t="n">
-        <v>0.65241</v>
+        <v>0.57735</v>
       </c>
       <c r="D12" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="F12" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3553</v>
+        <v>0.2837</v>
       </c>
       <c r="H12" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="J12" t="n">
         <v>0.1546</v>
@@ -2178,79 +2178,79 @@
         <v>37</v>
       </c>
       <c r="M12" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="N12" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6213</v>
+        <v>0.5367</v>
       </c>
       <c r="P12" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="R12" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="T12" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1773</v>
+        <v>1.0667</v>
       </c>
       <c r="V12" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="X12" t="n">
         <v>0.1546</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.4433</v>
+        <v>1.3197</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.959</v>
+        <v>0.8285</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.781</v>
+        <v>1.6115</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2700-10-10</t>
+          <t>2700-08-08-LN</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 7/8-14 x 7/8-14 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 3/4-16 x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>7/8-14</t>
+          <t>3/4-16</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>7/8-14 (bulkhead)</t>
+          <t>3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -2285,14 +2285,14 @@
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>2700-10-10</t>
+          <t>2700-LN-08-08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2700-10-10-LN</t>
+          <t>2700-10-10</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2700-10-10-LN</t>
+          <t>2700-10-10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 7/8-14 x 7/8-14 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 7/8-14 x 7/8-14 (bulkhead)</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2436,42 +2436,42 @@
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2700-LN-10-10</t>
+          <t>2700-10-10</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2700-12-12</t>
+          <t>2700-10-10-LN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.09</v>
+        <v>2.74</v>
       </c>
       <c r="C14" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D14" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="F14" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3895</v>
+        <v>0.3553</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="K14" t="n">
         <v>60</v>
@@ -2480,79 +2480,79 @@
         <v>37</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="N14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7045</v>
+        <v>0.6213</v>
       </c>
       <c r="P14" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="R14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="T14" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2755</v>
+        <v>1.1773</v>
       </c>
       <c r="V14" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.5905</v>
+        <v>1.4433</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.102</v>
+        <v>0.959</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.988</v>
+        <v>1.781</v>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2700-12-12</t>
+          <t>2700-10-10-LN</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 1/16-12 x 1 1/16-12 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 7/8-14 x 7/8-14 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>1 1/16-12</t>
+          <t>7/8-14</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>1 1/16-12 (bulkhead)</t>
+          <t>7/8-14 (bulkhead)</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -2587,14 +2587,14 @@
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2700-12-12</t>
+          <t>2700-LN-10-10</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2700-12-12-LN</t>
+          <t>2700-12-12</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>2700-12-12-LN</t>
+          <t>2700-12-12</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 1/16-12 x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 1/16-12 x 1 1/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2738,42 +2738,42 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>2700-LN-12-12</t>
+          <t>2700-12-12</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2700-16-12</t>
+          <t>2700-12-12-LN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="C16" t="n">
-        <v>0.94108</v>
+        <v>0.79674</v>
       </c>
       <c r="D16" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="E16" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="F16" t="n">
         <v>0.125</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4365</v>
+        <v>0.3895</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="K16" t="n">
         <v>60</v>
@@ -2782,13 +2782,13 @@
         <v>37</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="N16" t="n">
         <v>0.08333</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.7045</v>
       </c>
       <c r="P16" t="n">
         <v>0.04511</v>
@@ -2836,25 +2836,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.1505</v>
+        <v>1.102</v>
       </c>
       <c r="AG16" t="n">
         <v>0.61</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.9895</v>
+        <v>1.988</v>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2700-16-12</t>
+          <t>2700-12-12-LN</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/16-12 x 1 1/16-12 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 1/16-12 x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>1 5/16-12</t>
+          <t>1 1/16-12</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -2889,14 +2889,14 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2700-16-12</t>
+          <t>2700-LN-12-12</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2700-16-12-LN</t>
+          <t>2700-16-12</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -3000,12 +3000,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>2700-16-12-LN</t>
+          <t>2700-16-12</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/16-12 x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/16-12 x 1 1/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -3040,14 +3040,14 @@
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2700-LN-16-12</t>
+          <t>2700-16-12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2700-16-16</t>
+          <t>2700-16-12-LN</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3102,7 +3102,7 @@
         <v>0.08333</v>
       </c>
       <c r="S18" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="T18" t="n">
         <v>0.125</v>
@@ -3111,16 +3111,16 @@
         <v>1.2755</v>
       </c>
       <c r="V18" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="Z18" t="n">
         <v>0.08333</v>
@@ -3144,19 +3144,19 @@
         <v>1.1505</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AH18" t="n">
         <v>1.9895</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>2700-16-16</t>
+          <t>2700-16-12-LN</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/16-12 x 1 5/16-12 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/16-12 x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>1 5/16-12 (bulkhead)</t>
+          <t>1 1/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2700-16-16</t>
+          <t>2700-LN-16-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2700-16-16-LN</t>
+          <t>2700-16-16</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>2700-16-16-LN</t>
+          <t>2700-16-16</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/16-12 x 1 5/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/16-12 x 1 5/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -3342,42 +3342,42 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2700-LN-16-16</t>
+          <t>2700-16-16</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2700-20-20</t>
+          <t>2700-16-16-LN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.31</v>
+        <v>3.14</v>
       </c>
       <c r="C20" t="n">
-        <v>1.08542</v>
+        <v>0.94108</v>
       </c>
       <c r="D20" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="F20" t="n">
         <v>0.125</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4316</v>
+        <v>0.4365</v>
       </c>
       <c r="H20" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="K20" t="n">
         <v>60</v>
@@ -3386,13 +3386,13 @@
         <v>37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="N20" t="n">
         <v>0.08333</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7986</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="P20" t="n">
         <v>0.04511</v>
@@ -3404,31 +3404,31 @@
         <v>0.08333</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="T20" t="n">
         <v>0.125</v>
       </c>
       <c r="U20" t="n">
-        <v>1.2736</v>
+        <v>1.2755</v>
       </c>
       <c r="V20" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="X20" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="Z20" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.6406</v>
+        <v>1.5905</v>
       </c>
       <c r="AB20" t="n">
         <v>0.04511</v>
@@ -3440,25 +3440,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.234</v>
+        <v>1.1505</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.076</v>
+        <v>1.9895</v>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>2700-20-20</t>
+          <t>2700-16-16-LN</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/8-12 x 1 5/8-12 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/16-12 x 1 5/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -3468,12 +3468,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>1 5/8-12</t>
+          <t>1 5/16-12</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>1 5/8-12 (bulkhead)</t>
+          <t>1 5/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -3493,14 +3493,14 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>2700-20-20</t>
+          <t>2700-LN-16-16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2700-20-20-LN</t>
+          <t>2700-20-20</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>2700-20-20-LN</t>
+          <t>2700-20-20</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/8-12 x 1 5/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/8-12 x 1 5/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3644,42 +3644,42 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2700-LN-20-20</t>
+          <t>2700-20-20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2700-24-24</t>
+          <t>2700-20-20-LN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.52</v>
+        <v>3.31</v>
       </c>
       <c r="C22" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D22" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="F22" t="n">
         <v>0.125</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5454</v>
+        <v>0.4316</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="K22" t="n">
         <v>60</v>
@@ -3688,13 +3688,13 @@
         <v>37</v>
       </c>
       <c r="M22" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="N22" t="n">
         <v>0.08333</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9234</v>
+        <v>0.7986</v>
       </c>
       <c r="P22" t="n">
         <v>0.04511</v>
@@ -3706,31 +3706,31 @@
         <v>0.08333</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="T22" t="n">
         <v>0.125</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2724</v>
+        <v>1.2736</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="X22" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="Z22" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.6504</v>
+        <v>1.6406</v>
       </c>
       <c r="AB22" t="n">
         <v>0.04511</v>
@@ -3742,25 +3742,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.3965</v>
+        <v>1.234</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.1235</v>
+        <v>2.076</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2700-24-24</t>
+          <t>2700-20-20-LN</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 7/8-12 x 1 7/8-12 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 5/8-12 x 1 5/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>1 7/8-12</t>
+          <t>1 5/8-12</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>1 7/8-12 (bulkhead)</t>
+          <t>1 5/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -3795,14 +3795,14 @@
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>2700-24-24</t>
+          <t>2700-LN-20-20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2700-24-24-LN</t>
+          <t>2700-24-24</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2700-24-24-LN</t>
+          <t>2700-24-24</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 1 7/8-12 x 1 7/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 7/8-12 x 1 7/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3946,42 +3946,42 @@
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2700-LN-24-24</t>
+          <t>2700-24-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2700-32-32</t>
+          <t>2700-24-24-LN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="C24" t="n">
-        <v>1.58771</v>
+        <v>1.22976</v>
       </c>
       <c r="D24" t="n">
-        <v>2.75</v>
+        <v>2.13</v>
       </c>
       <c r="E24" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="F24" t="n">
         <v>0.125</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7124</v>
+        <v>0.5454</v>
       </c>
       <c r="H24" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="K24" t="n">
         <v>60</v>
@@ -3990,13 +3990,13 @@
         <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="N24" t="n">
         <v>0.08333</v>
       </c>
       <c r="O24" t="n">
-        <v>1.1734</v>
+        <v>0.9234</v>
       </c>
       <c r="P24" t="n">
         <v>0.04511</v>
@@ -4008,31 +4008,31 @@
         <v>0.08333</v>
       </c>
       <c r="S24" t="n">
-        <v>1.25</v>
+        <v>0.9375</v>
       </c>
       <c r="T24" t="n">
         <v>0.125</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4694</v>
+        <v>1.2724</v>
       </c>
       <c r="V24" t="n">
-        <v>1.19</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1292</v>
+        <v>0.1298</v>
       </c>
       <c r="X24" t="n">
-        <v>0.3318</v>
+        <v>0.2482</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.5</v>
+        <v>1.875</v>
       </c>
       <c r="Z24" t="n">
         <v>0.08333</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.9304</v>
+        <v>1.6504</v>
       </c>
       <c r="AB24" t="n">
         <v>0.04511</v>
@@ -4044,25 +4044,25 @@
         <v>0.08333</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.7215</v>
+        <v>1.3965</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.78</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.4785</v>
+        <v>2.1235</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>2700-32-32</t>
+          <t>2700-24-24-LN</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>Bulkhead Union (JIC x JIC bulkhead), 2 1/2-12 x 2 1/2-12 (bulkhead)</t>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 1 7/8-12 x 1 7/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -4072,12 +4072,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2 1/2-12</t>
+          <t>1 7/8-12</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2 1/2-12 (bulkhead)</t>
+          <t>1 7/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -4097,14 +4097,14 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>2700-32-32</t>
+          <t>2700-LN-24-24</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2700-32-32-LN</t>
+          <t>2700-32-32</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -4208,47 +4208,349 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
+          <t>2700-32-32</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 2 1/2-12 x 2 1/2-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>2 1/2-12</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Air-Way s72 (double-pass 27 rows; first pass claimed 30 - trap; survey said 24 - page wins); JIC ends VERIFIED (MS33656J); -LN rows ship with locknut, same dims | MODEL: JIC end A: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); the bulkhead is the SECOND dash (I1 = the bulkhead length of that dash on 2705/2706, e.g. 2700-06-04 I1 1.20 = -04); bore step at the hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr">
+        <is>
+          <t>bulkhead thread size/length and locknut geometry not tabulated on page - defer to MS51520 (untranscribed) or Brennan STEP -&gt; RESOLVED 2026-09-24 by the Brennan 2705-08-08 STEP: bulkhead thread = the JIC thread of that dash, run over the bulkhead length I1</t>
+        </is>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>2700-32-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>2700-32-32-LN</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="B26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.58771</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.7124</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="K26" t="n">
+        <v>60</v>
+      </c>
+      <c r="L26" t="n">
+        <v>37</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.1734</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.4694</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.9304</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.7215</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.4785</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>2700-32-32-LN</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
         <is>
           <t>Bulkhead Union (JIC x JIC bulkhead), 2 1/2-12 x 2 1/2-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
-      <c r="AK25" t="inlineStr">
+      <c r="AK26" t="inlineStr">
         <is>
           <t>2700</t>
         </is>
       </c>
-      <c r="AL25" t="inlineStr">
+      <c r="AL26" t="inlineStr">
         <is>
           <t>2 1/2-12</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
+      <c r="AM26" t="inlineStr">
         <is>
           <t>2 1/2-12 (bulkhead)</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
+      <c r="AN26" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AO26" t="inlineStr">
         <is>
           <t>Air-Way s72 (double-pass 27 rows; first pass claimed 30 - trap; survey said 24 - page wins); JIC ends VERIFIED (MS33656J); -LN rows ship with locknut, same dims | MODEL: JIC end A: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); the bulkhead is the SECOND dash (I1 = the bulkhead length of that dash on 2705/2706, e.g. 2700-06-04 I1 1.20 = -04); bore step at the hex mid-plane (ASSUMPTION, as 2403)</t>
         </is>
       </c>
-      <c r="AP25" t="inlineStr">
+      <c r="AP26" t="inlineStr">
         <is>
           <t>bulkhead thread size/length and locknut geometry not tabulated on page - defer to MS51520 (untranscribed) or Brennan STEP -&gt; RESOLVED 2026-09-24 by the Brennan 2705-08-08 STEP: bulkhead thread = the JIC thread of that dash, run over the bulkhead length I1</t>
         </is>
       </c>
-      <c r="AQ25" t="inlineStr">
+      <c r="AQ26" t="inlineStr">
         <is>
           <t>2700-LN-32-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2700-LN-02-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="K27" t="n">
+        <v>60</v>
+      </c>
+      <c r="L27" t="n">
+        <v>37</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.02255</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.01042</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.989</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.02255</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0.01042</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2700-LN-02-02</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>Bulkhead Union (JIC x JIC bulkhead), 5/16-24 x 5/16-24 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>5/16-24</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>5/16-24 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L4@DRIVE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "L LGTH" = "1.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - overall length [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; C2HEX@HEX: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "C HEX" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - body hex [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 12/13 rows with an Air-Way/OMi value agree with this catalog column to rounding (1 differ, e.g. 2700-06-04 0.69 vs 0.812); D1@BORE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "B1 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - bore end B1 [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; D2@BORE: Brennan TFA catalog p8 table TFA-p008-t03 "2700 MJ-MJ BULKHEAD STRAIGHT" row 2700-02-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 149.4, page verified) [Brennan = yes 2026-10-18] - bore end B2 (bulkhead) [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; mapping: TFA p8 2700 drawing: L = overall, C HEX = body hex, B1/B2 DRILL = bores (impact/F2a.json, certain); same-table check on today's base: 13/13 rows with an Air-Way/OMi value agree with this catalog column to rounding; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2700-02-02.stp (sha256 8510b8b0f1b648e7...) measured with wave2/straight/scripts/measure_bulkhead.py (prof.py section; validated: Brennan 2705-08-08 gives I1 1.44 = Air-Way): bulkhead tip 1.422 - relief start 0.352 (after the 0.04 collar) = 1.07; the -02 nose on the STEP = MS33656J JIC[2] (seat 0.1108, land 0.0662, relief 0.063); STEP overall 1.87 = catalog L 1.870, hex 0.5621 = catalog 0.562 [Brennan = yes 2026-10-18] [the -LN part = the plain 2700-02-02 + a locknut: Q-TRANSFER-LN open]; THDMAJ_B1@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (5/16-24); THDMAJ_B2@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major (5/16-24); $PRP@Threads: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread texts, format of the built 2700 rows | MODEL: JIC end A: MS33656J chain per dash (2403 table, VERIFIED vs Brennan); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); the bulkhead is the SECOND dash (I1 = the bulkhead length of that dash on 2705/2706, e.g. 2700-06-04 I1 1.20 = -04); bore step at the hex mid-plane (ASSUMPTION, as 2403)</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L4 / hex / bores from the Brennan TFA catalog p8, I1 measured on the Brennan 2700-02-02 STEP (no Air-Way -02 bulkhead) - copied from the plain part (Q-TRANSFER-LN)</t>
+        </is>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>2700-LN-02-02</t>
         </is>
       </c>
     </row>
